--- a/dados/tabela_dispersao_final.xlsx
+++ b/dados/tabela_dispersao_final.xlsx
@@ -458,47 +458,50 @@
         </is>
       </c>
       <c r="D2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rao Spacing</t>
+          <t>Hermans-Rasson</t>
         </is>
       </c>
       <c r="F2">
-        <v>266.0869565217391</v>
+        <v>18.4519</v>
+      </c>
+      <c r="G2">
+        <v>0.0001</v>
       </c>
       <c r="H2">
         <v>0.297</v>
       </c>
       <c r="I2">
-        <v>3.807</v>
+        <v>3.59</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10/08/22</t>
+          <t>28/07/22</t>
         </is>
       </c>
       <c r="K2">
-        <v>0.457</v>
+        <v>0.465</v>
       </c>
       <c r="L2">
-        <v>0.511</v>
+        <v>0.712</v>
       </c>
       <c r="M2">
-        <v>3.598</v>
+        <v>3.606</v>
       </c>
       <c r="N2">
-        <v>13.324</v>
+        <v>12.929</v>
       </c>
       <c r="O2">
         <v>0.5</v>
       </c>
       <c r="P2">
-        <v>151.513</v>
+        <v>135.123</v>
       </c>
       <c r="Q2">
-        <v>0.317</v>
+        <v>0.458</v>
       </c>
     </row>
     <row r="3">
@@ -526,10 +529,10 @@
         </is>
       </c>
       <c r="F3">
-        <v>0.3918013161422812</v>
+        <v>0.3918</v>
       </c>
       <c r="G3">
-        <v>0.001544150042785009</v>
+        <v>0.0015</v>
       </c>
       <c r="H3">
         <v>0.392</v>
@@ -576,11 +579,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rao Spacing</t>
+          <t>Hermans-Rasson</t>
         </is>
       </c>
       <c r="F4">
-        <v>240</v>
+        <v>5.523</v>
+      </c>
+      <c r="G4">
+        <v>0.1148</v>
       </c>
       <c r="H4">
         <v>0.053</v>
